--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T20:14:11+00:00</t>
+    <t>2026-09-14T10:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T10:47:12+00:00</t>
+    <t>2026-09-14T11:35:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:35:30+00:00</t>
+    <t>2026-09-14T12:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:58:37+00:00</t>
+    <t>2026-09-14T13:24:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:24:58+00:00</t>
+    <t>2026-09-14T13:41:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:41:44+00:00</t>
+    <t>2026-09-14T14:16:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
